--- a/Tableau_synthese.xlsx
+++ b/Tableau_synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davidsword\Desktop\portefolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F4EF55-4FC9-4C2E-B67A-66154A342A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE82F5D-DC12-4C4D-84DC-4DC1379644C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
-  </si>
-  <si>
-    <t xml:space="preserve">N° candidat : </t>
   </si>
   <si>
     <t xml:space="preserve">Centre de formation : CFA UTEC </t>
@@ -139,6 +136,9 @@
   </si>
   <si>
     <t>Adresse URL du portfolio : https://davidsword80.github.io/PorteFolio/</t>
+  </si>
+  <si>
+    <t>N° candidat : 02148557833</t>
   </si>
 </sst>
 </file>
@@ -675,15 +675,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -715,30 +739,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1060,124 +1060,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>25</v>
+      <c r="A3" s="23" t="s">
+        <v>24</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="42" t="s">
-        <v>3</v>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="29" t="s">
+        <v>26</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="43"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="30"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="19" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="B6" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="32"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="20" t="s">
+      <c r="D7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="E7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="F7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="G7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="H7" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>21</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1216,16 +1216,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>22</v>
+      <c r="A8" s="33" t="s">
+        <v>21</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1713,16 +1713,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>23</v>
+      <c r="A19" s="36" t="s">
+        <v>22</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="30"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="38"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2075,16 +2075,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
-        <v>24</v>
+      <c r="A27" s="36" t="s">
+        <v>23</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="30"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2529,11 +2529,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2541,6 +2536,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2551,6 +2551,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="363344d2-291b-4101-a50e-4c4e57e06257" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a807daf-f98a-479d-9d0b-ee2628977d16">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DB353BCD07693D458C93E8F49DE3128F" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="0496c8411046d64edd6d4ed77808098b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a807daf-f98a-479d-9d0b-ee2628977d16" xmlns:ns3="363344d2-291b-4101-a50e-4c4e57e06257" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3c8e84541775c1fe23b57a8b70498bfe" ns2:_="" ns3:_="">
     <xsd:import namespace="1a807daf-f98a-479d-9d0b-ee2628977d16"/>
@@ -2745,17 +2756,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="363344d2-291b-4101-a50e-4c4e57e06257" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a807daf-f98a-479d-9d0b-ee2628977d16">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2766,6 +2766,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA077FCB-4FFB-4B93-8A01-96823A39740E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="363344d2-291b-4101-a50e-4c4e57e06257"/>
+    <ds:schemaRef ds:uri="1a807daf-f98a-479d-9d0b-ee2628977d16"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{957D750A-F46D-47D5-9418-EAE24789DA6D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2784,17 +2795,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA077FCB-4FFB-4B93-8A01-96823A39740E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="363344d2-291b-4101-a50e-4c4e57e06257"/>
-    <ds:schemaRef ds:uri="1a807daf-f98a-479d-9d0b-ee2628977d16"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC4CE58-9CCF-48FE-84F7-281BF600C5F0}">
   <ds:schemaRefs>

--- a/Tableau_synthese.xlsx
+++ b/Tableau_synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davidsword\Desktop\portefolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE82F5D-DC12-4C4D-84DC-4DC1379644C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C2BDB6-C116-413E-809D-D7BDA674C1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Option :</t>
-  </si>
-  <si>
-    <t>▢ SISR</t>
   </si>
   <si>
     <t>▢ SLAM</t>
@@ -139,6 +136,60 @@
   </si>
   <si>
     <t>N° candidat : 02148557833</t>
+  </si>
+  <si>
+    <t>☒ SISR</t>
+  </si>
+  <si>
+    <t>Infrastructure Proxmox — Épreuve E6</t>
+  </si>
+  <si>
+    <t>Mise en place d'une caméra de surveillance WiFi (E6 — Fiche 1)</t>
+  </si>
+  <si>
+    <t>Déploiement d'un site web sur réseau local (E6 — Fiche 2)</t>
+  </si>
+  <si>
+    <t>Certification RGPD — L'Atelier CNIL</t>
+  </si>
+  <si>
+    <t>Certification Cisco — Introduction to Cybersecurity</t>
+  </si>
+  <si>
+    <t>Création d'une veille technologique — Cloud Hybride &amp; IA</t>
+  </si>
+  <si>
+    <t>Refonte interface support Freshdesk → Gespage</t>
+  </si>
+  <si>
+    <t>Gestion du ticketing (support helpdesk N1/N2)</t>
+  </si>
+  <si>
+    <t>Dépannage à distance des clients</t>
+  </si>
+  <si>
+    <t>Prise de contrôle à distance d'une borne (SSH / TeamViewer)</t>
+  </si>
+  <si>
+    <t>Démantèlement de bornes de lavage</t>
+  </si>
+  <si>
+    <t>Apprentissage des pièces pour les monnayeurs</t>
+  </si>
+  <si>
+    <t>Logiciel SSH — Automatisation bornes de lavage</t>
+  </si>
+  <si>
+    <t>Mise en place d'un VPN pour accès sécurisé à distance</t>
+  </si>
+  <si>
+    <t>Création de documentation technique pour l'équipe</t>
+  </si>
+  <si>
+    <t>Programmation d'un modem de communication</t>
+  </si>
+  <si>
+    <t>Mise en place d'un nouveau module de communication bancaire</t>
   </si>
 </sst>
 </file>
@@ -148,7 +199,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -206,7 +257,12 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -610,7 +666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -636,12 +692,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -651,95 +701,114 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1060,124 +1129,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="30"/>
+      <c r="A3" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="34"/>
+      <c r="H3" s="40"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="12" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="19" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="32"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="20"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="20" t="s">
+      <c r="D7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="E7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="F7" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="G7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="H7" s="18" t="s">
         <v>19</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>20</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1216,16 +1285,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="A8" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1262,15 +1331,19 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="48">
+        <v>45901</v>
+      </c>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1307,15 +1380,17 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1352,15 +1427,17 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="42"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1397,15 +1474,17 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="42"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1442,15 +1521,17 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="42"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1487,15 +1568,17 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="16"/>
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="42"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1533,14 +1616,14 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
+      <c r="A15" s="45"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1578,14 +1661,13 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="42"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1623,14 +1705,14 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="42"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1668,14 +1750,14 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="42"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1713,16 +1795,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
+      <c r="A19" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1759,15 +1841,17 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="44" t="s">
+        <v>34</v>
+      </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="13"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1804,15 +1888,17 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="44" t="s">
+        <v>35</v>
+      </c>
       <c r="B21" s="8"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="13"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1849,15 +1935,17 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="B22" s="8"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="13"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1894,15 +1982,17 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="44" t="s">
+        <v>38</v>
+      </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="13"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -1939,15 +2029,17 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="13"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -1984,15 +2076,17 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="44" t="s">
+        <v>42</v>
+      </c>
       <c r="B25" s="8"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="13"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2030,14 +2124,14 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
+      <c r="A26" s="46"/>
       <c r="B26" s="8"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="13"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2075,16 +2169,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
+      <c r="A27" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2121,15 +2215,17 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="44" t="s">
+        <v>33</v>
+      </c>
       <c r="B28" s="8"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="13"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2166,15 +2262,17 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="44" t="s">
+        <v>37</v>
+      </c>
       <c r="B29" s="8"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="16"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="13"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2211,15 +2309,17 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="44" t="s">
+        <v>39</v>
+      </c>
       <c r="B30" s="8"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="16"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="13"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2256,15 +2356,17 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="44" t="s">
+        <v>40</v>
+      </c>
       <c r="B31" s="8"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="16"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="13"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2301,15 +2403,17 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="44" t="s">
+        <v>43</v>
+      </c>
       <c r="B32" s="8"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="16"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="13"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2347,14 +2451,14 @@
       <c r="AQ32"/>
     </row>
     <row r="33" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
+      <c r="A33" s="46"/>
       <c r="B33" s="8"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="16"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="13"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2392,14 +2496,14 @@
       <c r="AQ33"/>
     </row>
     <row r="34" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="15"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -2529,6 +2633,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2536,32 +2645,16 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="363344d2-291b-4101-a50e-4c4e57e06257" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a807daf-f98a-479d-9d0b-ee2628977d16">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DB353BCD07693D458C93E8F49DE3128F" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="0496c8411046d64edd6d4ed77808098b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a807daf-f98a-479d-9d0b-ee2628977d16" xmlns:ns3="363344d2-291b-4101-a50e-4c4e57e06257" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3c8e84541775c1fe23b57a8b70498bfe" ns2:_="" ns3:_="">
     <xsd:import namespace="1a807daf-f98a-479d-9d0b-ee2628977d16"/>
@@ -2756,6 +2849,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="363344d2-291b-4101-a50e-4c4e57e06257" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a807daf-f98a-479d-9d0b-ee2628977d16">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2766,17 +2870,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA077FCB-4FFB-4B93-8A01-96823A39740E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="363344d2-291b-4101-a50e-4c4e57e06257"/>
-    <ds:schemaRef ds:uri="1a807daf-f98a-479d-9d0b-ee2628977d16"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{957D750A-F46D-47D5-9418-EAE24789DA6D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2795,6 +2888,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA077FCB-4FFB-4B93-8A01-96823A39740E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="363344d2-291b-4101-a50e-4c4e57e06257"/>
+    <ds:schemaRef ds:uri="1a807daf-f98a-479d-9d0b-ee2628977d16"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC4CE58-9CCF-48FE-84F7-281BF600C5F0}">
   <ds:schemaRefs>
